--- a/Eval_results/District_stats/district_global/summary.xlsx
+++ b/Eval_results/District_stats/district_global/summary.xlsx
@@ -476,29 +476,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>丰台区</t>
+          <t>Fengtai</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48.96937346458435</v>
+        <v>48.96936893463135</v>
       </c>
       <c r="D2" t="n">
-        <v>59.96855630725622</v>
+        <v>59.9687515348196</v>
       </c>
       <c r="E2" t="n">
-        <v>2.961883544921875</v>
+        <v>56.38446807861328</v>
       </c>
       <c r="F2" t="n">
-        <v>111.8998133167624</v>
+        <v>165.3225885480642</v>
       </c>
       <c r="G2" t="n">
-        <v>48969373464.58435</v>
+        <v>48969368934.63135</v>
       </c>
       <c r="H2" t="n">
-        <v>59.96855630725622</v>
+        <v>59.9687515348196</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00423126220703125</v>
+        <v>0.08054924011230469</v>
       </c>
     </row>
     <row r="3">
@@ -507,29 +507,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>剩余五区</t>
+          <t>Remaining</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.410776208620518</v>
+        <v>1.410776506643742</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05100911855697632</v>
+        <v>-0.05100910551846027</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02111752954078838</v>
+        <v>-4.163646697998047</v>
       </c>
       <c r="F3" t="n">
-        <v>1.380884619604331</v>
+        <v>-2.803879296872765</v>
       </c>
       <c r="G3" t="n">
-        <v>1410776208.620518</v>
+        <v>1410776506.643742</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.05100911855697632</v>
+        <v>-0.05100910551846027</v>
       </c>
       <c r="I3" t="n">
-        <v>3.01678993439834e-05</v>
+        <v>-0.005948066711425781</v>
       </c>
     </row>
     <row r="4">
@@ -538,29 +538,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大兴区</t>
+          <t>Daxing</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.44611056149006</v>
+        <v>25.44610889256001</v>
       </c>
       <c r="D4" t="n">
-        <v>8.20673905313015</v>
+        <v>8.206739172339439</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4499880676157773</v>
+        <v>12.92686462402344</v>
       </c>
       <c r="F4" t="n">
-        <v>34.10283768223599</v>
+        <v>46.57971268892288</v>
       </c>
       <c r="G4" t="n">
-        <v>25446110561.49006</v>
+        <v>25446108892.56001</v>
       </c>
       <c r="H4" t="n">
-        <v>8.20673905313015</v>
+        <v>8.206739172339439</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006428400965939675</v>
+        <v>0.01846694946289062</v>
       </c>
     </row>
     <row r="5">
@@ -569,29 +569,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>房山区</t>
+          <t>Fangshan</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.6813600808382</v>
+        <v>12.68135845661163</v>
       </c>
       <c r="D5" t="n">
-        <v>28.56738391518593</v>
+        <v>28.56735160946846</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6104723792523146</v>
+        <v>202.9919624328613</v>
       </c>
       <c r="F5" t="n">
-        <v>41.85921637527645</v>
+        <v>244.2406724989414</v>
       </c>
       <c r="G5" t="n">
-        <v>12681360080.8382</v>
+        <v>12681358456.61163</v>
       </c>
       <c r="H5" t="n">
-        <v>28.56738391518593</v>
+        <v>28.56735160946846</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008721033989318779</v>
+        <v>0.2899885177612305</v>
       </c>
     </row>
     <row r="6">
@@ -600,29 +600,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>昌平区</t>
+          <t>Changping</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31.0540048442781</v>
+        <v>31.05400256440043</v>
       </c>
       <c r="D6" t="n">
-        <v>80.93691825866699</v>
+        <v>80.93672323226929</v>
       </c>
       <c r="E6" t="n">
-        <v>3.118540551513433</v>
+        <v>185.3250026702881</v>
       </c>
       <c r="F6" t="n">
-        <v>115.1094636544585</v>
+        <v>297.3157284669578</v>
       </c>
       <c r="G6" t="n">
-        <v>31054004844.2781</v>
+        <v>31054002564.40043</v>
       </c>
       <c r="H6" t="n">
-        <v>80.93691825866699</v>
+        <v>80.93672323226929</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004455057930733477</v>
+        <v>0.2647500038146973</v>
       </c>
     </row>
     <row r="7">
@@ -631,29 +631,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>朝阳区</t>
+          <t>Chaoyang</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.05777297914028</v>
+        <v>55.05776619911194</v>
       </c>
       <c r="D7" t="n">
-        <v>35.77148509025574</v>
+        <v>35.77148465812206</v>
       </c>
       <c r="E7" t="n">
-        <v>3.685798645019531</v>
+        <v>42.41585731506348</v>
       </c>
       <c r="F7" t="n">
-        <v>94.51505671441555</v>
+        <v>133.2451081722975</v>
       </c>
       <c r="G7" t="n">
-        <v>55057772979.14028</v>
+        <v>55057766199.11194</v>
       </c>
       <c r="H7" t="n">
-        <v>35.77148509025574</v>
+        <v>35.77148465812206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005265426635742187</v>
+        <v>0.06059408187866211</v>
       </c>
     </row>
     <row r="8">
@@ -662,29 +662,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>海淀区</t>
+          <t>Haidian</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>65.12017464637756</v>
+        <v>65.12017178535461</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.540690006688237</v>
+        <v>-5.540527136996388</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8922328222543</v>
+        <v>-4.784154891967773</v>
       </c>
       <c r="F8" t="n">
-        <v>61.47171746194363</v>
+        <v>54.79548975639045</v>
       </c>
       <c r="G8" t="n">
-        <v>65120174646.37756</v>
+        <v>65120171785.35461</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.540690006688237</v>
+        <v>-5.540527136996388</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002703189746077572</v>
+        <v>-0.006834506988525391</v>
       </c>
     </row>
     <row r="9">
@@ -693,29 +693,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>通州区</t>
+          <t>Tongzhou</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11.71947204321623</v>
+        <v>11.71947249025106</v>
       </c>
       <c r="D9" t="n">
-        <v>2.304752505384386</v>
+        <v>2.304882979020476</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3272883212193847</v>
+        <v>-3.224040985107422</v>
       </c>
       <c r="F9" t="n">
-        <v>14.35151286982</v>
+        <v>10.80031448416412</v>
       </c>
       <c r="G9" t="n">
-        <v>11719472043.21623</v>
+        <v>11719472490.25106</v>
       </c>
       <c r="H9" t="n">
-        <v>2.304752505384386</v>
+        <v>2.304882979020476</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000467554744599121</v>
+        <v>-0.004605772835867746</v>
       </c>
     </row>
     <row r="10">
@@ -724,29 +724,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>顺义区</t>
+          <t>Shunyi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.6899821460247</v>
+        <v>15.68998086452484</v>
       </c>
       <c r="D10" t="n">
-        <v>11.60651907324791</v>
+        <v>11.60649487376213</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2173169502057135</v>
+        <v>496.7236480712891</v>
       </c>
       <c r="F10" t="n">
-        <v>27.51381816947833</v>
+        <v>524.020123809576</v>
       </c>
       <c r="G10" t="n">
-        <v>15689982146.0247</v>
+        <v>15689980864.52484</v>
       </c>
       <c r="H10" t="n">
-        <v>11.60651907324791</v>
+        <v>11.60649487376213</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003104527860081622</v>
+        <v>0.7096052115304129</v>
       </c>
     </row>
   </sheetData>
